--- a/PEAK_Programme_Template.xlsx
+++ b/PEAK_Programme_Template.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R455525ce8db8486b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Info" sheetId="2" r:id="R134282856e6a4403"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercises" sheetId="3" r:id="Ra45ee1f4d0044b29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="4" r:id="Rc61234c6afca4cb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training Rules" sheetId="5" r:id="R6a9f7d8d3faa4c96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RPE Lookup" sheetId="6" r:id="R48d3163f8c374acb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Re573027a0be94dc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Programme Info" sheetId="2" r:id="R28d2f8c17b164100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercises" sheetId="3" r:id="R7952bc21e9f04851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sessions" sheetId="4" r:id="Re47739ac246f4ce3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training Rules" sheetId="5" r:id="Rb507c8e748e349d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RPE Lookup" sheetId="6" r:id="Ra00744869fd449db"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -47,7 +47,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -89,6 +89,26 @@
         <x:fgColor rgb="FFEDF5F3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF123047"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7F4F0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF103243"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF15324E"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -97,7 +117,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -121,6 +141,26 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -323,13 +363,13 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="100" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>PEAK / TRAINING — EXCEL PROGRAMME TEMPLATE</x:v>
+        <x:v>PEAK / TRAINING — EXCEL PROGRAMME TEMPLATE v5</x:v>
       </x:c>
       <x:c r="B1" s="3" t="str"/>
     </x:row>
@@ -459,6 +499,62 @@
       </x:c>
       <x:c r="B17" s="10" t="str">
         <x:v>Export a full JSON backup before modifying a programme or resetting your browser.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="32" customHeight="1">
+      <x:c r="A18" s="31" t="str">
+        <x:v>SET TYPES</x:v>
+      </x:c>
+      <x:c r="B18" s="32" t="str">
+        <x:v>On the Sessions sheet, leave Set type blank for STANDARD, or select AMRAP or REP_MAX.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="32" customHeight="1">
+      <x:c r="A19" s="31" t="str">
+        <x:v>STANDARD</x:v>
+      </x:c>
+      <x:c r="B19" s="32" t="str">
+        <x:v>Barbell working/ramp set: Reps and Percent 1RM required. Load is calculated from this programme's movement maximums.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="31" t="str">
+        <x:v>AMRAP</x:v>
+      </x:c>
+      <x:c r="B20" s="32" t="str">
+        <x:v>Barbell set: Reps = minimum target; enter Target weight kg. Log actual weight and actual reps (reps may exceed target). Percent 1RM not required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="32" customHeight="1">
+      <x:c r="A21" s="31" t="str">
+        <x:v>REP_MAX</x:v>
+      </x:c>
+      <x:c r="B21" s="32" t="str">
+        <x:v>Barbell set: Reps = goal rep count; enter Goal weight kg. Log actual weight and actual reps. Percent 1RM not required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="32" customHeight="1">
+      <x:c r="A22" s="31" t="str">
+        <x:v>EXAMPLE ROWS</x:v>
+      </x:c>
+      <x:c r="B22" s="32" t="str">
+        <x:v>Sessions rows 28–29 show an AMRAP attempt and a rep-max attempt. Delete or change these examples when creating your programme.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="32" customHeight="1">
+      <x:c r="A23" s="31" t="str">
+        <x:v>PER-PROGRAM MAXES</x:v>
+      </x:c>
+      <x:c r="B23" s="32" t="str">
+        <x:v>Each enrolled programme maintains independent movement maxes in PEAK &gt; Settings. The values in Programme Info are starting defaults.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="41" customHeight="1">
+      <x:c r="A24" s="34" t="str">
+        <x:v>RPE EXEMPTIONS</x:v>
+      </x:c>
+      <x:c r="B24" s="32" t="str">
+        <x:v>Exercises → RPE cap applies: No removes RPE-cap calculation and hides the actual RPE input for that movement. Leave Yes (or blank) to apply the default cap.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -570,9 +666,10 @@
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
+    <x:row r="1" ht="27" customHeight="1">
       <x:c r="A1" s="13" t="str">
         <x:v>Code</x:v>
       </x:c>
@@ -593,6 +690,9 @@
       </x:c>
       <x:c r="G1" s="13" t="str">
         <x:v>RPE offset</x:v>
+      </x:c>
+      <x:c r="H1" s="34" t="str">
+        <x:v>RPE cap applies</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -617,6 +717,9 @@
       <x:c r="G2" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H2" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="18" t="str">
@@ -640,6 +743,9 @@
       <x:c r="G3" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H3" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="18" t="str">
@@ -663,6 +769,9 @@
       <x:c r="G4" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H4" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="18" t="str">
@@ -686,6 +795,9 @@
       <x:c r="G5" s="18" t="n">
         <x:v>1.25</x:v>
       </x:c>
+      <x:c r="H5" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="18" t="str">
@@ -709,6 +821,9 @@
       <x:c r="G6" s="18" t="n">
         <x:v>0.45</x:v>
       </x:c>
+      <x:c r="H6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="18" t="str">
@@ -732,6 +847,9 @@
       <x:c r="G7" s="18" t="n">
         <x:v>0.85</x:v>
       </x:c>
+      <x:c r="H7" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="18" t="str">
@@ -755,6 +873,9 @@
       <x:c r="G8" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H8" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="18" t="str">
@@ -778,6 +899,9 @@
       <x:c r="G9" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H9" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="18" t="str">
@@ -801,14 +925,20 @@
       <x:c r="G10" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H10" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="C2:C200">
       <x:formula1>"BAR,ACC"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="D2:D200">
       <x:formula1>"SQ,BP,DL,ACC"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H2:H400">
+      <x:formula1>"Yes,No"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -833,6 +963,9 @@
     <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="17" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="19" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -878,6 +1011,15 @@
       <x:c r="N1" s="13" t="str">
         <x:v>RIR</x:v>
       </x:c>
+      <x:c r="O1" s="27" t="str">
+        <x:v>Set type</x:v>
+      </x:c>
+      <x:c r="P1" s="27" t="str">
+        <x:v>Target weight kg</x:v>
+      </x:c>
+      <x:c r="Q1" s="27" t="str">
+        <x:v>Goal weight kg</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="21" customHeight="1">
       <x:c r="A2" t="n">
@@ -1859,10 +2001,95 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Preparation</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Accessory / technical</x:v>
+      </x:c>
+      <x:c r="E28"/>
+      <x:c r="F28" t="str">
+        <x:v>SQ</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>WORK</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>w1d4-sq-amrap-demo</x:v>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J28"/>
+      <x:c r="K28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L28"/>
+      <x:c r="M28"/>
+      <x:c r="N28"/>
+      <x:c r="O28" s="28" t="str">
+        <x:v>AMRAP</x:v>
+      </x:c>
+      <x:c r="P28" s="28" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="Q28" s="28"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Preparation</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>Accessory / technical</x:v>
+      </x:c>
+      <x:c r="E29"/>
+      <x:c r="F29" t="str">
+        <x:v>BP</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>WORK</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>w1d4-bp-repmax-demo</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J29"/>
+      <x:c r="K29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L29"/>
+      <x:c r="M29"/>
+      <x:c r="N29"/>
+      <x:c r="O29" s="28" t="str">
+        <x:v>REP_MAX</x:v>
+      </x:c>
+      <x:c r="P29" s="28"/>
+      <x:c r="Q29" s="28" t="n">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="G2:G500">
       <x:formula1>"RAMP,WORK,ACC,REST"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="O2:O1000">
+      <x:formula1>"STANDARD,AMRAP,REP_MAX"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
